--- a/data/processed/ontology/controlled_vocabulary.xlsx
+++ b/data/processed/ontology/controlled_vocabulary.xlsx
@@ -12,7 +12,7 @@
     <sheet name="effect_vocabulary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="subject_authority_scope" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="metric_vocabulary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="condition_exception_scope_fragments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="modifier_fragments" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3356,7 +3356,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3394,7 +3398,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3432,7 +3440,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3470,7 +3482,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3508,7 +3524,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3546,7 +3566,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3584,7 +3608,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3622,7 +3650,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3660,7 +3692,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3698,7 +3734,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3736,7 +3776,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3774,7 +3818,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3812,7 +3860,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3850,7 +3902,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3888,7 +3944,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3926,7 +3986,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3964,7 +4028,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4002,7 +4070,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4040,7 +4112,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4078,7 +4154,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4116,7 +4196,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4154,7 +4238,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4192,7 +4280,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4230,7 +4322,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4268,7 +4364,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4306,7 +4406,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4344,7 +4448,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4382,7 +4490,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4420,7 +4532,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4458,7 +4574,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4496,7 +4616,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4534,7 +4658,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4572,7 +4700,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4610,7 +4742,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4648,7 +4784,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4686,7 +4826,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4724,7 +4868,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4762,7 +4910,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4800,7 +4952,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4838,7 +4994,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4876,7 +5036,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4914,7 +5078,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4952,7 +5120,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4990,7 +5162,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5028,7 +5204,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5066,7 +5246,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5104,7 +5288,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5142,7 +5330,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5180,7 +5372,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5218,7 +5414,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5256,7 +5456,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5294,7 +5498,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5332,7 +5540,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5370,7 +5582,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5408,7 +5624,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5446,7 +5666,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5484,7 +5708,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5522,7 +5750,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5560,7 +5792,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5598,7 +5834,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5636,7 +5876,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5674,7 +5918,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5712,7 +5960,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5750,7 +6002,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5788,7 +6044,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5826,7 +6086,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5864,7 +6128,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5902,7 +6170,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5940,7 +6212,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5978,7 +6254,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6016,7 +6296,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6054,7 +6338,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6092,7 +6380,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6130,7 +6422,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6168,7 +6464,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6206,7 +6506,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6244,7 +6548,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6282,7 +6590,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6320,7 +6632,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6358,7 +6674,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6396,7 +6716,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6434,7 +6758,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6472,7 +6800,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6510,7 +6842,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6604,7 +6940,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6642,7 +6982,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6680,7 +7024,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6718,7 +7066,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6756,7 +7108,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6794,7 +7150,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6874,7 +7234,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6912,7 +7276,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6950,7 +7318,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6988,7 +7360,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7026,7 +7402,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7064,7 +7444,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7102,7 +7486,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7140,7 +7528,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7178,7 +7570,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7216,7 +7612,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7254,7 +7654,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7292,7 +7696,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7330,7 +7738,11 @@
           <t>trung_binh</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7368,7 +7780,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7406,7 +7822,11 @@
           <t>trung_binh</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7444,7 +7864,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7482,7 +7906,11 @@
           <t>trung_binh</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7520,7 +7948,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7558,7 +7990,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7596,7 +8032,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7634,7 +8074,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7756,7 +8200,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7794,7 +8242,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7832,7 +8284,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7870,7 +8326,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7908,7 +8368,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7946,7 +8410,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7984,7 +8452,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8022,7 +8494,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8060,7 +8536,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8098,7 +8578,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8136,7 +8620,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8174,7 +8662,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8212,7 +8704,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8292,7 +8788,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8330,7 +8830,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8368,7 +8872,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8406,7 +8914,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8444,7 +8956,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8482,7 +8998,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8520,7 +9040,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8558,7 +9082,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8596,7 +9124,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8634,7 +9166,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8672,7 +9208,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8710,7 +9250,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8748,7 +9292,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8828,7 +9376,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8866,7 +9418,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8904,7 +9460,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8942,7 +9502,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8980,7 +9544,11 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -11223,7 +11791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11263,706 +11831,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>effect_vocabulary</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>duoc_cap_giay_chung_nhan_dang_ky_doanh_nghiep_tru_truong_hop_dieu_le_cong_ty_hoac_hop_dong_dang_ky_mua_co_phan_quy_dinh_mot_thoi_han_khac_ngan_hon</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>tru_truong_hop_dieu_le_cong_ty_hoac_hop_dong_dang_ky_mua_co_phan_quy_dinh_mot_thoi_han_khac_ngan_hon</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>được cấp Giấy chứng nhận đăng ký doanh nghiệp, trừ trường hợp Điều lệ công ty hoặc hợp đồng đăng ký mua cổ phần quy định một thời hạn khác ngắn hơn</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>tach_exception_condition_khoi_effect</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D113_K1_E000082_H67FF516B0336__b18dfb4fdee692; RULE_LUATDN_D113_K1_E000083_H4135AC48C5CC__92ac27f8e80f5c; RULE_LUATDN_D113_K1_E000361_H9559D7A7E175__e7c07124cb07f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>effect_vocabulary</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>cong_ty_cap_nhat_kip_thoi_thay_doi_co_dong_trong_so_dang_ky_co_dong_theo_yeu_cau_cua_co_dong_co_lien_quan</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>theo_yeu_cau_cua_co_dong_co_lien_quan</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Công ty cập nhật kịp thời thay đổi cổ đông trong sổ đăng ký cổ đông theo yêu cầu của cổ đông có liên quan</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>tach_exception_condition_khoi_effect</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D122_K5_E000112_H7EB788490A1F__103fee3c3acdd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>effect_vocabulary</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>cap_giay_chung_nhan_dang_ky_doanh_nghiep_neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>cấp Giấy chứng nhận đăng ký doanh nghiệp nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>tach_exception_condition_khoi_effect</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D205_K2_E000171_HC103AB968CE3__db7af93bea0162</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>effect_vocabulary</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>cap_giay_chung_nhan_dang_ky_doanh_nghiep_neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghie</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghie</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>cấp Giấy chứng nhận đăng ký doanh nghiệp nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệ</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>tach_exception_condition_khoi_effect</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D205_K2_E000376_HDE4D11047D02__d8fcb45eefe40d</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>effect_vocabulary</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>cap_giay_chung_nhan_dang_ky_doanh_nghiep_neu_co_du_dieu_kien_quy</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>neu_co_du_dieu_kien_quy</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>cấp Giấy chứng nhận đăng ký doanh nghiệp nếu có đủ điều kiện quy</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>tach_exception_condition_khoi_effect</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D205_K2_E000174_HBB868040B12A__747ded761e8875</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>effect_vocabulary</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>cong_ty_cap_nhat_kip_thoi_thay_doi_thanh_vien_trong_so_dang_ky_thanh_vien_theo_yeu_cau_cua_thanh_vien_co_lien_quan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>theo_yeu_cau_cua_thanh_vien_co_lien_quan</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Công ty cập nhật kịp thời thay đổi thành viên trong sổ đăng ký thành viên theo yêu cầu của thành viên có liên quan</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>tach_exception_condition_khoi_effect</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D48_K3_E000054_H7C5394B2A508__0618df5626c3cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>effect_vocabulary</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>chap_thuan_thi_co_quan_dang_ky_kinh_doanh_cap_xa_ra_quyet_dinh_thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>chấp thuận thì Cơ quan đăng ký kinh doanh cấp xã ra quyết định thu hồi Giấy chứng nhận đăng ký hộ kinh doanh trong thời hạn 03 ngày làm việc kể từ ngày kết thúc thời hạn</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>tach_exception_condition_khoi_effect</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D107_K4_E000323_HC7780C522732__8b02a06325d0fb; RULE_ND168_D107_K4_E000503_HAD9534ACA4E3__80fbe079a9ef2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>effect_vocabulary</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han_giai_trinh</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han_giai_trinh</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh trong thời hạn 03 ngày làm việc kể từ ngày kết thúc thời hạn giải trình</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>tach_exception_condition_khoi_effect</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D107_K4_E000502_HAD9534ACA4E3__ff40d9db87e1fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>effect_vocabulary</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh_van_phong_dai_dien_trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han_giai_trinh</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han_giai_trinh</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>thu hồi Giấy chứng nhận đăng ký hoạt động chi nhánh, văn phòng đại diện trong thời hạn 03 ngày làm việc kể từ ngày kết thúc thời hạn giải trình</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>tach_exception_condition_khoi_effect</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D71_K3_E000496_HD4B75A6952A5__ca660bf58d6b4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>effect_vocabulary</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>chap_thuan_thi_co_quan_dang_ky_kinh_doanh_cap_tinh_ra_quyet_dinh_thu_hoi_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh_van_phong_dai_dien_trong_thoi_han_03_ngay_lam_viec_k</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>trong_thoi_han_03_ngay_lam_viec_k</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>chấp thuận thì Cơ quan đăng ký kinh doanh cấp tỉnh ra quyết định thu hồi Giấy chứng nhận đăng ký hoạt động chi nhánh, văn phòng đại diện trong thời hạn 03 ngày làm việc k</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>tach_exception_condition_khoi_effect</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D71_K3_E000497_HD4B75A6952A5__7fe9ff563fe49f</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>discourse_or_condition</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>object_vocabulary</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>phai_co_cac_giay_to_sau_day</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>phải có các giấy tờ sau đây | phải có các giấy tờ sau đây:</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>loai_condition_hoac_scope_khoi_object</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D28_K7_E000248_H189EC3F188B6__506b814bf616a9; RULE_ND168_D28_K7_E000410_HAB891EF8FB58__9c53376c4e0d7b; RULE_ND168_D28_K7_E000409_HAB891EF8FB58__b4611058cb4d7c; RULE_ND168_D28_K7_E000411_HAB891EF8FB58__9271c5cad72e01</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>discourse_or_condition</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>object_vocabulary</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>khi_dang_ky_thanh_lap_doanh_nghiep</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>khi đăng ký thành lập doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>loai_condition_hoac_scope_khoi_object</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D120_K2_E000110_H2F74D053E9ED__e3455c07586f9b; RULE_LUATDN_D120_K2_E000106_H50EB455F10E0__d9e773edb1f1e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>discourse_or_condition</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>object_vocabulary</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>khi_trinh_dai_hoi_dong_co_dong_xem_xet</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>khi trình Đại hội đồng cổ đông xem xét</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>loai_condition_hoac_scope_khoi_object</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D175_K2_E000122_H3A810D8013F8__cecb075395e7d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>discourse_or_condition</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>object_vocabulary</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>hop_dong_da_ky_voi_khach_hang_va_nguoi_lao_dong</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>hợp đồng đã ký với khách hàng và người lao động</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>loai_condition_hoac_scope_khoi_object</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D206_K3_E000183_HB3760B0CD551__fa214a6f1d0709</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>discourse_or_condition</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>object_vocabulary</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>tru_truong_hop_doanh_nghiep</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>trừ trường hợp doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>loai_condition_hoac_scope_khoi_object</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D206_K3_E000184_HB3760B0CD551__d9cc7b2a45cf2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>discourse_or_condition</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>object_vocabulary</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>hop_dong_da_ky_voi_khach_hang_va_nguoi_lao_dong_tru_truong_hop_doanh_nghiep_chu_no_khach_hang_va_nguoi</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>hợp đồng đã ký với khách hàng và người lao động, trừ trường hợp doanh nghiệp, chủ nợ, khách hàng và người</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>loai_condition_hoac_scope_khoi_object</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D206_K3_E000182_HB3760B0CD551__0c3013b06a8c7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>discourse_or_condition</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>object_vocabulary</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>khi_thay_doi_noi_dung_giay_chung_nhan_dang_ky_doanh_nghiep_quy_dinh_tai_dieu_28_cua_luat_nay</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>khi thay đổi nội dung Giấy chứng nhận đăng ký doanh nghiệp quy định tại Điều 28 của Luật này</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>loai_condition_hoac_scope_khoi_object</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>RULE_LUATDN_D30_K1_E000020_H4E002511683E__bc79ef05e292ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>discourse_or_condition</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>object_vocabulary</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>khi_ho_so_dang_ky_doanh_nghiep_chua_duoc_chap_thuan_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>khi hồ sơ đăng ký doanh nghiệp chưa được chấp thuận trên Hệ thống thông tin quốc gia về đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>loai_condition_hoac_scope_khoi_object</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D31_K6_E000267_H565D1BB5E0AC__243ed69455d8ce; RULE_ND168_D31_K6_E000271_H565D1BB5E0AC__515f331279a5a7; RULE_ND168_D31_K6_E000416_HF58B712D1CE4__7867763b848ee0; RULE_ND168_D31_K6_E000419_H46A4A566E7A4__38e6cb2ba88b0e; RULE_ND168_D31_K6_E000421_H46A4A566E7A4__0907921944a235</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>discourse_or_condition</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>object_vocabulary</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>truong_hop_doanh_nghiep_cap_nhat</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>trường hợp doanh nghiệp cập nhật</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>loai_condition_hoac_scope_khoi_object</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D57_K3_E000299_HA471205F1C6F__44c27f4eae6de3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>discourse_or_condition</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>object_vocabulary</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>van_ban_giai_trinh_cua_doanh_nghiep_ve_ly_do_dang_ky_thay_doi_kem_ho_so_dang_ky_thay_doi_khi_dang_ky_phuc_vu_giai_the</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi (kèm hồ sơ đăng ký thay đổi khi đăng ký phục vụ giải thể)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>loai_condition_hoac_scope_khoi_object</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D59_K2_B_E000479_H6CE5F7A93C8B__e80d74b1b90e68; RULE_ND168_D59_K2_B_E000480_H6CE5F7A93C8B__56e9128f42f85d</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/processed/ontology/controlled_vocabulary.xlsx
+++ b/data/processed/ontology/controlled_vocabulary.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2614,17 +2614,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>cong_ty_cap_nhat_kip_thoi_thay_doi_co_dong_trong_so_dang_ky_co_dong</t>
+          <t>cong_ty_cap_nhat_kip_thoi_thay_doi_co_dong_trong_so_dang_ky_co_dong_theo_yeu_cau_cua_co_dong_co_lien_quan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>chuyen_tu_effect:cong_ty_cap_nhat_kip_thoi_thay_doi_co_dong_trong_so_dang_ky_co_dong</t>
+          <t>chuyen_tu_effect:cong_ty_cap_nhat_kip_thoi_thay_doi_co_dong_trong_so_dang_ky_co_dong_theo_yeu_cau_cua_co_dong_co_lien_quan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `cong_ty_cap_nhat_kip_thoi_thay_doi_co_dong_trong_so_dang_ky_co_dong_theo_yeu_cau_cua_co_dong_co_lien_quan`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `cong_ty_cap_nhat_kip_thoi_thay_doi_co_dong_trong_so_dang_ky_co_dong_theo_yeu_cau_cua_co_dong_co_lien_quan`.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `cong_ty_gui_ve_cong_ty_phieu_lay_y_kien`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `cong_ty_gui_ve_cong_ty_phieu_lay_y_kien`.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `cong_ty_cap_nhat_danh_sach_nhung_nguoi_co_lien_quan_cua_cong_ty`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `cong_ty_cap_nhat_danh_sach_nhung_nguoi_co_lien_quan_cua_cong_ty`.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `co_quan_dang_ky_kinh_doanh_xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `co_quan_dang_ky_kinh_doanh_xem_xet_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep`.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `co_quan_dang_ky_kinh_doanh_xem_xet_tinh_hop_le_cua_ho_so_dang_ky_doanh_nghiep_va_cap_dang_ky_doanh_nghiep`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `co_quan_dang_ky_kinh_doanh_xem_xet_tinh_hop_le_cua_ho_so_dang_ky_doanh_nghiep_va_cap_dang_ky_doanh_nghiep`.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `co_quan_dang_ky_kinh_doanh_xem_xet_tinh_hop_le_cua_ho_so_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep_moi`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `co_quan_dang_ky_kinh_doanh_xem_xet_tinh_hop_le_cua_ho_so_va_cap_giay_chung_nhan_dang_ky_doanh_nghiep_moi`.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>co_quan_dang_ky_kinh_doanh_cap_thong_tin_duoc_luu_giu_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_phai_nop_phi</t>
+          <t>duoc_cap_thong_tin_duoc_luu_giu_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_phai_nop_phi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>chuyen_tu_effect:co_quan_dang_ky_kinh_doanh_cap_thong_tin_duoc_luu_giu_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_phai_nop_phi</t>
+          <t>chuyen_tu_effect:duoc_cap_thong_tin_duoc_luu_giu_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_phai_nop_phi</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `co_quan_dang_ky_kinh_doanh_cap_thong_tin_duoc_luu_giu_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_phai_nop_phi`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `duoc_cap_thong_tin_duoc_luu_giu_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_phai_nop_phi`.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2943,17 +2943,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>co_quan_dang_ky_kinh_doanh_xem_xet_tinh_hop_le_cua_ho_so_va_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
+          <t>co_quan_dang_ky_kinh_doanh_cap_thong_tin_duoc_luu_giu_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_phai_nop_phi</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>chuyen_tu_effect:co_quan_dang_ky_kinh_doanh_xem_xet_tinh_hop_le_cua_ho_so_va_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
+          <t>chuyen_tu_effect:co_quan_dang_ky_kinh_doanh_cap_thong_tin_duoc_luu_giu_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_phai_nop_phi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `co_quan_dang_ky_kinh_doanh_xem_xet_tinh_hop_le_cua_ho_so_va_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `co_quan_dang_ky_kinh_doanh_cap_thong_tin_duoc_luu_giu_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_phai_nop_phi`.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D45_K3_E000041_H54A3724FA902__05e1c142b45446</t>
+          <t>RULE_LUATDN_D33_K1_E000040_HBD0F2B965340__e0be59d28bca43</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>cong_ty_cap_nhat_kip_thoi_thay_doi_thanh_vien_trong_so_dang_ky_thanh_vien</t>
+          <t>co_quan_dang_ky_kinh_doanh_xem_xet_tinh_hop_le_cua_ho_so_va_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>chuyen_tu_effect:cong_ty_cap_nhat_kip_thoi_thay_doi_thanh_vien_trong_so_dang_ky_thanh_vien</t>
+          <t>chuyen_tu_effect:co_quan_dang_ky_kinh_doanh_xem_xet_tinh_hop_le_cua_ho_so_va_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `cong_ty_cap_nhat_kip_thoi_thay_doi_thanh_vien_trong_so_dang_ky_thanh_vien_theo_yeu_cau_cua_thanh_vien_co_lien_quan`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `co_quan_dang_ky_kinh_doanh_xem_xet_tinh_hop_le_cua_ho_so_va_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh`.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D48_K3_E000054_H7C5394B2A508__0618df5626c3cd</t>
+          <t>RULE_LUATDN_D45_K3_E000041_H54A3724FA902__05e1c142b45446</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3037,17 +3037,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>cong_ty_gui_phieu_lay_y_kien_ve_cong_ty</t>
+          <t>cong_ty_cap_nhat_kip_thoi_thay_doi_thanh_vien_trong_so_dang_ky_thanh_vien_theo_yeu_cau_cua_thanh_vien_co_lien_quan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>chuyen_tu_effect:cong_ty_gui_phieu_lay_y_kien_ve_cong_ty</t>
+          <t>chuyen_tu_effect:cong_ty_cap_nhat_kip_thoi_thay_doi_thanh_vien_trong_so_dang_ky_thanh_vien_theo_yeu_cau_cua_thanh_vien_co_lien_quan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `cong_ty_gui_phieu_lay_y_kien_ve_cong_ty`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `cong_ty_cap_nhat_kip_thoi_thay_doi_thanh_vien_trong_so_dang_ky_thanh_vien_theo_yeu_cau_cua_thanh_vien_co_lien_quan`.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D61_K3_D_E000058_H55FDA829DADB__3659a9a3d4de76</t>
+          <t>RULE_LUATDN_D48_K3_E000054_H7C5394B2A508__0618df5626c3cd</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3084,17 +3084,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>cong_ty_truoc_hoi_dong_thanh_vien_ve_viec_thuc_hien_quyen_va_nghia_vu_cua_minh</t>
+          <t>cong_ty_gui_phieu_lay_y_kien_ve_cong_ty</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>chuyen_tu_effect:cong_ty_truoc_hoi_dong_thanh_vien_ve_viec_thuc_hien_quyen_va_nghia_vu_cua_minh</t>
+          <t>chuyen_tu_effect:cong_ty_gui_phieu_lay_y_kien_ve_cong_ty</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `cong_ty_truoc_hoi_dong_thanh_vien_ve_viec_thuc_hien_quyen_va_nghia_vu_cua_minh`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `cong_ty_gui_phieu_lay_y_kien_ve_cong_ty`.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D63_K1_E000063_H87D3F0FBD99C__bad2ab5e0b47d7</t>
+          <t>RULE_LUATDN_D61_K3_D_E000058_H55FDA829DADB__3659a9a3d4de76</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>co_quan_dang_ky_kinh_doanh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+          <t>cong_ty_truoc_hoi_dong_thanh_vien_ve_viec_thuc_hien_quyen_va_nghia_vu_cua_minh</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>chuyen_tu_effect:co_quan_dang_ky_kinh_doanh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+          <t>chuyen_tu_effect:cong_ty_truoc_hoi_dong_thanh_vien_ve_viec_thuc_hien_quyen_va_nghia_vu_cua_minh</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `co_quan_dang_ky_kinh_doanh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `cong_ty_truoc_hoi_dong_thanh_vien_ve_viec_thuc_hien_quyen_va_nghia_vu_cua_minh`.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RULE_ND168_D31_K3_E000266_H1509A1A35C79__4bce78214f31d1; RULE_ND168_D41_K2_E000273_H906A9A038A6C__f824edde05271e; RULE_ND168_D42_K2_E000275_H821D573EEDF4__530e6c2ac4eb1f; RULE_ND168_D43_K5_E000277_H0243FD848FE3__802b6f2206ab87; RULE_ND168_D44_K5_E000279_HCA503CFECDA8__aa2d89008e4cec</t>
+          <t>RULE_LUATDN_D63_K1_E000063_H87D3F0FBD99C__bad2ab5e0b47d7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3178,17 +3178,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>co_quan_dang_ky_kinh_doanh_cap_tinh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+          <t>chap_thuan_thi_co_quan_dang_ky_kinh_doanh_cap_xa_ra_quyet_dinh_thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>chuyen_tu_effect:co_quan_dang_ky_kinh_doanh_cap_tinh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+          <t>chuyen_tu_effect:chap_thuan_thi_co_quan_dang_ky_kinh_doanh_cap_xa_ra_quyet_dinh_thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `co_quan_dang_ky_kinh_doanh_cap_tinh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so`.</t>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `chap_thuan_thi_co_quan_dang_ky_kinh_doanh_cap_xa_ra_quyet_dinh_thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han`.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>RULE_ND168_D31_K3_E000415_HF96DE9D9BF08__715810e59d4772; RULE_ND168_D41_K2_E000425_HEEADD79DF7E1__341dcc712fe43d; RULE_ND168_D42_K2_E000430_H871CDC7A0EBD__6112b7ae8b0e38; RULE_ND168_D43_K5_E000435_HADF045408BC9__6a55deefc5885c; RULE_ND168_D44_K5_E000440_H3776FA482E45__895dd1b8852a0c</t>
+          <t>RULE_ND168_D107_K4_E000323_HC7780C522732__8b02a06325d0fb; RULE_ND168_D107_K4_E000503_HAD9534ACA4E3__80fbe079a9ef2a</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3225,40 +3225,228 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>co_quan_dang_ky_kinh_doanh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>chuyen_tu_effect:co_quan_dang_ky_kinh_doanh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `co_quan_dang_ky_kinh_doanh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so`.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>mapping_hanh_vi_khong_phai_ket_qua</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>RULE_ND168_D31_K3_E000266_H1509A1A35C79__4bce78214f31d1; RULE_ND168_D41_K2_E000273_H906A9A038A6C__f824edde05271e; RULE_ND168_D42_K2_E000275_H821D573EEDF4__530e6c2ac4eb1f; RULE_ND168_D43_K5_E000277_H0243FD848FE3__802b6f2206ab87; RULE_ND168_D44_K5_E000279_HCA503CFECDA8__aa2d89008e4cec</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>chuyen_action_ra_khoi_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>hanh_vi</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>co_quan_dang_ky_kinh_doanh_cap_tinh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>chuyen_tu_effect:co_quan_dang_ky_kinh_doanh_cap_tinh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `co_quan_dang_ky_kinh_doanh_cap_tinh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so`.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>mapping_hanh_vi_khong_phai_ket_qua</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>RULE_ND168_D31_K3_E000415_HF96DE9D9BF08__715810e59d4772; RULE_ND168_D41_K2_E000425_HEEADD79DF7E1__341dcc712fe43d; RULE_ND168_D42_K2_E000430_H871CDC7A0EBD__6112b7ae8b0e38; RULE_ND168_D43_K5_E000435_HADF045408BC9__6a55deefc5885c; RULE_ND168_D44_K5_E000440_H3776FA482E45__895dd1b8852a0c</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>chuyen_action_ra_khoi_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>hanh_vi</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>nguoi_thanh_lap_doanh_nghiep_thuc_hien_day_du</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>chuyen_tu_effect:nguoi_thanh_lap_doanh_nghiep_thuc_hien_day_du</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). Gốc: `nguoi_thanh_lap_doanh_nghiep_thuc_hien_day_du`.</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `nguoi_thanh_lap_doanh_nghiep_thuc_hien_day_du`.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>mapping_hanh_vi_khong_phai_ket_qua</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>RULE_ND168_D5_K2_E000197_HA0ABBF5F3EF2__802411e0d0015e</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>co</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>trung_binh</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>chuyen_action_ra_khoi_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>hanh_vi</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>cham_dut_hoat_dong_chi_nhanh_doanh_nghiep_phai_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_c</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>chuyen_tu_effect:cham_dut_hoat_dong_chi_nhanh_doanh_nghiep_phai_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_c</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `cham_dut_hoat_dong_chi_nhanh_doanh_nghiep_phai_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_c`.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>mapping_hanh_vi_khong_phai_ket_qua</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>RULE_ND168_D66_K5_E000304_HF34F2F907D78__50796ed7bced1b; RULE_ND168_D66_K5_E000483_H87A2DB73760C__e6f80f3364ef77</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>chuyen_action_ra_khoi_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>hanh_vi</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>cham_dut_hoat_dong_chi_nhanh_doanh_nghiep_phai_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan_dang_ky_kinh_doanh_cap_tinh_noi_dat_dia</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>chuyen_tu_effect:cham_dut_hoat_dong_chi_nhanh_doanh_nghiep_phai_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan_dang_ky_kinh_doanh_cap_tinh_noi_dat_dia</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Diễn đạt hành vi/thủ tục (đưa khỏi effect). `cham_dut_hoat_dong_chi_nhanh_doanh_nghiep_phai_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan_dang_ky_kinh_doanh_cap_tinh</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>mapping_hanh_vi_khong_phai_ket_qua</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>RULE_ND168_D66_K5_E000482_H87A2DB73760C__0abeaa88313a85</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>chuyen_action_ra_khoi_effect</t>
         </is>
@@ -3323,7 +3511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3356,16 +3544,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3398,11 +3582,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3440,11 +3620,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3482,11 +3658,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3524,11 +3696,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3566,16 +3734,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>giao_dich</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3608,16 +3772,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>giao_dich</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3650,11 +3810,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3692,11 +3848,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3734,16 +3886,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>nghia_vu_tai_san</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3776,11 +3924,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3818,11 +3962,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3860,16 +4000,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3902,11 +4038,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3944,16 +4076,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>giao_dich</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3986,11 +4114,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4028,11 +4152,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4070,16 +4190,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4112,16 +4228,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4154,11 +4266,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4196,16 +4304,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4238,16 +4342,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4280,16 +4380,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>thong_tin</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4322,11 +4418,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4364,16 +4456,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4406,16 +4494,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>co_phan_thanh_vien</t>
+          <t>thanh_vien</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4448,11 +4532,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4490,11 +4570,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4532,16 +4608,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>co_phan_thanh_vien</t>
+          <t>thanh_vien</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4574,11 +4646,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4616,16 +4684,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>von_gop_von</t>
+          <t>von</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4658,11 +4722,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4700,11 +4760,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4742,16 +4798,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4784,11 +4836,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4826,16 +4874,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4868,11 +4912,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4910,16 +4950,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4952,16 +4988,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4994,16 +5026,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5036,11 +5064,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5078,16 +5102,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5120,16 +5140,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5162,16 +5178,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5204,16 +5216,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5246,16 +5254,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5288,16 +5292,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5330,16 +5330,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5372,16 +5368,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5414,16 +5406,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5456,16 +5444,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5498,16 +5482,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5540,16 +5520,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5582,16 +5558,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5624,16 +5596,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5666,16 +5634,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5708,11 +5672,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5750,16 +5710,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5792,16 +5748,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5834,16 +5786,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>von</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5876,16 +5824,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5918,16 +5862,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>thong_tin</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5960,16 +5900,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6002,16 +5938,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6044,16 +5976,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6086,16 +6014,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6128,11 +6052,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6170,11 +6090,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6212,16 +6128,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6254,16 +6166,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6296,16 +6204,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6338,16 +6242,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6380,16 +6280,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6422,16 +6318,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6464,16 +6356,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6506,16 +6394,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>giay_chung_nhan</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6548,16 +6432,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>ho_so</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6590,16 +6470,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>noi_dung_dang_ky</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6632,11 +6508,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6674,11 +6546,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6716,16 +6584,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>noi_dung_dang_ky</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6758,16 +6622,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6800,16 +6660,12 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ho_so_tai_lieu</t>
+          <t>danh_sach</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6842,11 +6698,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6859,7 +6711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6940,11 +6792,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6982,11 +6830,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7024,11 +6868,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7066,11 +6906,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7108,11 +6944,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7150,11 +6982,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7234,11 +7062,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7276,11 +7100,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7318,11 +7138,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7360,11 +7176,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7402,11 +7214,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7444,11 +7252,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7486,11 +7290,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7528,11 +7328,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7570,11 +7366,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7612,11 +7404,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7631,7 +7419,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>chấm dứt hoạt động</t>
+          <t>chấm dứt hoạt động đối với chi nhánh; văn phòng đại diện; địa điểm kinh doanh; chấm dứt hoạt động</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7641,22 +7429,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RULE_ND168_D27_K3_B_E000408_H645CC4278C14__726aecd2fd98e0</t>
+          <t>RULE_ND168_D118_K3_E000522_H0811C24751E0__7fb44d85940b04; RULE_ND168_D118_K3_E000341_H6839229D9C6F__6f008278ee22c6; RULE_ND168_D27_K3_B_E000408_H645CC4278C14__726aecd2fd98e0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>cao</t>
+          <t>trung_binh</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>tach_condition_khoi_effect</t>
         </is>
       </c>
     </row>
@@ -7668,22 +7456,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cham_dut_hoat_dong_chi_nhanh_doanh_nghiep_phai_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_c</t>
+          <t>cham_dut_hoat_dong_chiu_trach_nhiem_thuc_hien_cac_hop_dong_thanh_toan_cac_khoan_no_gom_ca_no_thue_cua_chi_nhanh_va_t</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>chấm dứt hoạt động chi nhánh, doanh nghiệp phải thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc c</t>
+          <t>chấm dứt hoạt động chịu trách nhiệm thực hiện các hợp đồng, thanh toán các khoản nợ, gồm cả nợ thuế của chi nhánh và t</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_chi_nhanh_doanh_nghiep_phai_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_c`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_chiu_trach_nhiem_thuc_hien_cac_hop_dong_thanh_toan_cac_khoan_no_gom_ca_no_thue_cua_chi_nhanh_va_t`.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RULE_ND168_D66_K5_E000304_HF34F2F907D78__50796ed7bced1b; RULE_ND168_D66_K5_E000483_H87A2DB73760C__e6f80f3364ef77</t>
+          <t>RULE_LUATDN_D213_K3_E000191_HF074DD2CC305__cd4b8a1e04da78</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -7696,11 +7484,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7710,22 +7494,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cham_dut_hoat_dong_chi_nhanh_doanh_nghiep_phai_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan_dang_ky_kinh_doanh_cap_tinh_noi_dat_dia</t>
+          <t>cham_dut_hoat_dong_chiu_trach_nhiem_thuc_hien_cac_hop_dong_thanh_toan_cac_khoan_no_gom_ca_no_thue_cua_chi_nhanh_va_tiep_tuc_su_dung_lao_dong_hoac_giai_quyet_du_quyen_loi_hop_phap_cho_ngu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>chấm dứt hoạt động chi nhánh, doanh nghiệp phải thực hiện thủ tục chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan đăng ký kinh doanh cấp tỉnh nơi đặt địa</t>
+          <t>chấm dứt hoạt động chịu trách nhiệm thực hiện các hợp đồng, thanh toán các khoản nợ, gồm cả nợ thuế của chi nhánh và tiếp tục sử dụng lao động hoặc giải quyết đủ quyền lợi hợp pháp cho ngư</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_chi_nhanh_doanh_nghiep_phai_thuc_hien_thu_tuc_cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan_dang_ky_kinh_doanh_cap_tinh_noi_dat_di</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_chiu_trach_nhiem_thuc_hien_cac_hop_dong_thanh_toan_cac_khoan_no_gom_ca_no_thue_cua_chi_nhanh_va_tiep_tuc_su_dung_lao_dong_hoac_giai_quyet_du_quyen_loi_hop_phap_cho_ngu</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RULE_ND168_D66_K5_E000482_H87A2DB73760C__0abeaa88313a85</t>
+          <t>RULE_LUATDN_D213_K3_E000380_H8F80CAF77D48__c1b4b55e3b1389; RULE_LUATDN_D213_K3_E000189_HF074DD2CC305__1bbabbdbe86f35</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -7738,11 +7522,7 @@
           <t>trung_binh</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7752,22 +7532,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cham_dut_hoat_dong_chiu_trach_nhiem_thuc_hien_cac_hop_dong_thanh_toan_cac_khoan_no_gom_ca_no_thue_cua_chi_nhanh_va_t</t>
+          <t>cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan_dang_ky_kinh_doanh</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>chấm dứt hoạt động chịu trách nhiệm thực hiện các hợp đồng, thanh toán các khoản nợ, gồm cả nợ thuế của chi nhánh và t</t>
+          <t>chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_chiu_trach_nhiem_thuc_hien_cac_hop_dong_thanh_toan_cac_khoan_no_gom_ca_no_thue_cua_chi_nhanh_va_t`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan_dang_ky_kinh_doanh`.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D213_K3_E000191_HF074DD2CC305__cd4b8a1e04da78</t>
+          <t>RULE_ND168_D66_K5_E000303_HF34F2F907D78__8430406cf71e7d</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -7780,11 +7560,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7794,22 +7570,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cham_dut_hoat_dong_chiu_trach_nhiem_thuc_hien_cac_hop_dong_thanh_toan_cac_khoan_no_gom_ca_no_thue_cua_chi_nhanh_va_tiep_tuc_su_dung_lao_dong_hoac_giai_quyet_du_quyen_loi_hop_phap_cho_ngu</t>
+          <t>cham_dut_hoat_dong_trong_co_so_du_lieu_ve_dang_ky_ho_kinh_doanh</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>chấm dứt hoạt động chịu trách nhiệm thực hiện các hợp đồng, thanh toán các khoản nợ, gồm cả nợ thuế của chi nhánh và tiếp tục sử dụng lao động hoặc giải quyết đủ quyền lợi hợp pháp cho ngư</t>
+          <t>chấm dứt hoạt động trong Cơ sở dữ liệu về đăng ký hộ kinh doanh</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_chiu_trach_nhiem_thuc_hien_cac_hop_dong_thanh_toan_cac_khoan_no_gom_ca_no_thue_cua_chi_nhanh_va_tiep_tuc_su_dung_lao_dong_hoac_giai_quyet_du_quyen_loi_hop_phap_cho_ngu</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_trong_co_so_du_lieu_ve_dang_ky_ho_kinh_doanh`.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D213_K3_E000380_H8F80CAF77D48__c1b4b55e3b1389; RULE_LUATDN_D213_K3_E000189_HF074DD2CC305__1bbabbdbe86f35</t>
+          <t>RULE_ND168_D27_K3_B_E000407_H645CC4278C14__48dee7f15d2346</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7819,39 +7595,35 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>trung_binh</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cham_dut</t>
+          <t>chap_thuan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cham_dut_hoat_dong_cua_ho_kinh_doanh_cho_co_quan_thue_va_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut</t>
+          <t>chap_thuan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>chấm dứt hoạt động của hộ kinh doanh cho Cơ quan thuế và ra thông báo về việc hộ kinh doanh đang làm thủ tục chấm dứt</t>
+          <t>chấp thuận; trừ trường hợp Hội đồng thành viên quyết định thời hạn khác</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_cua_ho_kinh_doanh_cho_co_quan_thue_va_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `chap_thuan`.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RULE_ND168_D27_K3_B_E000406_H645CC4278C14__ca5b42fe13202c</t>
+          <t>RULE_LUATDN_D186_K1_E000124_HFF0DAB317E93__e594e48a541eab; RULE_ND168_D59_K2_B_E000479_H6CE5F7A93C8B__e80d74b1b90e68; RULE_ND168_D59_K2_B_E000301_HB765E274CC42__e48ea797ee3048; RULE_LUATDN_D186_K2_E000128_H978952EE6FD4__271a076b3bf9cb; RULE_LUATDN_D186_K2_E000364_HC305BFE2E363__e1e8bea05ff736; RULE_LUATDN_D186_K2_E000125_H2FC30FD46A92__59df9f03b09822</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7866,34 +7638,34 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>tach_exception_khoi_effect</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cham_dut</t>
+          <t>chap_thuan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cham_dut_hoat_dong_cua_ho_kinh_doanh_cho_co_quan_thue_va_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_tren_cong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_chuyen</t>
+          <t>chap_thuan_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>chấm dứt hoạt động của hộ kinh doanh cho Cơ quan thuế và ra thông báo về việc hộ kinh doanh đang làm thủ tục chấm dứt hoạt động trên Cổng thông tin quốc gia về đăng ký doanh nghiệp, chuyển</t>
+          <t>chấp thuận trên Hệ thống thông tin quốc gia về đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_cua_ho_kinh_doanh_cho_co_quan_thue_va_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_tren_cong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_chuye</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `chap_thuan_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep`.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RULE_ND168_D27_K3_B_E000405_H645CC4278C14__2da370c26df78e</t>
+          <t>RULE_ND168_D31_K6_E000267_H565D1BB5E0AC__243ed69455d8ce; RULE_ND168_D31_K6_E000271_H565D1BB5E0AC__515f331279a5a7; RULE_ND168_D31_K6_E000416_HF58B712D1CE4__7867763b848ee0; RULE_ND168_D31_K6_E000419_H46A4A566E7A4__38e6cb2ba88b0e</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7903,39 +7675,35 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>trung_binh</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cham_dut</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan_dang_ky_kinh_doanh</t>
+          <t>co_quan_dang_ky_kinh_doanh_ap_dung_quy_dinh_loai_tru</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>chấm dứt hoạt động của tất cả địa điểm kinh doanh trực thuộc chi nhánh tại Cơ quan đăng ký kinh doanh</t>
+          <t>Cơ quan đăng ký kinh doanh áp dụng quy định loại trừ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_cua_tat_ca_dia_diem_kinh_doanh_truc_thuoc_chi_nhanh_tai_co_quan_dang_ky_kinh_doanh`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `co_quan_dang_ky_kinh_doanh_ap_dung_quy_dinh_loai_tru`.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RULE_ND168_D66_K5_E000303_HF34F2F907D78__8430406cf71e7d</t>
+          <t>RULE_ND168_D20_K1_A_E000232_HEBA6CEE992E3__33783bcc8ca8c9</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -7948,36 +7716,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cham_dut</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>cham_dut_hoat_dong_doi_voi_chi_nhanh_van_phong_dai_dien_dia_diem_kinh_doanh</t>
+          <t>co_quan_dang_ky_kinh_doanh_cap_dang_ky_doanh_nghiep_theo_quy_trinh_du_phong</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>chấm dứt hoạt động đối với chi nhánh, văn phòng đại diện, địa điểm kinh doanh</t>
+          <t>Cơ quan đăng ký kinh doanh cấp đăng ký doanh nghiệp theo quy trình dự phòng</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_doi_voi_chi_nhanh_van_phong_dai_dien_dia_diem_kinh_doanh`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `co_quan_dang_ky_kinh_doanh_cap_dang_ky_doanh_nghiep_theo_quy_trinh_du_phong`.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RULE_ND168_D118_K3_E000522_H0811C24751E0__7fb44d85940b04; RULE_ND168_D118_K3_E000341_H6839229D9C6F__6f008278ee22c6</t>
+          <t>RULE_ND168_D13_K4_E000222_H7575F6E0A298__e3b2e7405f1543</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -7990,36 +7754,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cham_dut</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>cham_dut_hoat_dong_trong_co_so_du_lieu_ve_dang_ky_ho_kinh_doanh</t>
+          <t>co_quan_dang_ky_kinh_doanh_cap_tinh_thuc_hien_quan_ly_nha_nuoc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>chấm dứt hoạt động trong Cơ sở dữ liệu về đăng ký hộ kinh doanh</t>
+          <t>Cơ quan đăng ký kinh doanh cấp tỉnh thực hiện quản lý nhà nước</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `cham_dut_hoat_dong_trong_co_so_du_lieu_ve_dang_ky_ho_kinh_doanh`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `co_quan_dang_ky_kinh_doanh_cap_tinh_thuc_hien_quan_ly_nha_nuoc`.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RULE_ND168_D27_K3_B_E000407_H645CC4278C14__48dee7f15d2346</t>
+          <t>RULE_LUATDN_D215_K2_E000192_HA15EAD4E7536__4a0d8250bffec5</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -8032,36 +7792,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chap_thuan</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>chap_thuan</t>
+          <t>co_quan_dang_ky_kinh_doanh_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>chấp thuận</t>
+          <t>Cơ quan đăng ký kinh doanh đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `chap_thuan`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `co_quan_dang_ky_kinh_doanh_dang_ky_doanh_nghiep`.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D186_K1_E000124_HFF0DAB317E93__e594e48a541eab; RULE_ND168_D59_K2_B_E000479_H6CE5F7A93C8B__e80d74b1b90e68; RULE_ND168_D59_K2_B_E000301_HB765E274CC42__e48ea797ee3048</t>
+          <t>RULE_ND168_D20_K1_A_E000234_H8752DA9084F2__4600286e438dc3; RULE_ND168_D20_K1_A_E000230_HA78F4CA68C80__0e0c127de64957</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8074,120 +7830,108 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>chap_thuan_thi_co_quan_dang_ky_kinh_doanh_cap_tinh_ra_quyet_dinh_thu_hoi_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh_van_phong_dai_dien</t>
+          <t>co_quan_dang_ky_kinh_doanh_thanh_phan_ho_so</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>chấp thuận thì Cơ quan đăng ký kinh doanh cấp tỉnh ra quyết định thu hồi Giấy chứng nhận đăng ký hoạt động chi nhánh, văn phòng đại diện trong thời hạn 03 ngày làm việc k</t>
+          <t>Cơ quan đăng ký kinh doanh thành phần hồ sơ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `chap_thuan_thi_co_quan_dang_ky_kinh_doanh_cap_tinh_ra_quyet_dinh_thu_hoi_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh_van_phong_dai_dien`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `co_quan_dang_ky_kinh_doanh_thanh_phan_ho_so`.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RULE_ND168_D71_K3_E000497_HD4B75A6952A5__7fe9ff563fe49f</t>
+          <t>RULE_ND168_D15_K4_E000226_H77B8473A5144__f4a8cfe63d7a31</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>trung_binh</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>tach_condition_khoi_effect</t>
-        </is>
-      </c>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>thu_hoi</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>chap_thuan_thi_co_quan_dang_ky_kinh_doanh_cap_xa_ra_quyet_dinh_thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh</t>
+          <t>doanh_nghiep_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>chấp thuận thì Cơ quan đăng ký kinh doanh cấp xã ra quyết định thu hồi Giấy chứng nhận đăng ký hộ kinh doanh trong thời hạn 03 ngày làm việc kể từ ngày kết thúc thời hạn</t>
+          <t>Doanh nghiệp đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `chap_thuan_thi_co_quan_dang_ky_kinh_doanh_cap_xa_ra_quyet_dinh_thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `doanh_nghiep_dang_ky_doanh_nghiep`.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RULE_ND168_D107_K4_E000323_HC7780C522732__8b02a06325d0fb; RULE_ND168_D107_K4_E000503_HAD9534ACA4E3__80fbe079a9ef2a</t>
+          <t>RULE_ND168_D23_K1_K_E000238_H9F0055EDAC32__8b171c4fe8e666; RULE_ND168_D4_K5_E000194_H71B013782AB6__fe65a55a4c30bb</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>khong</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>trung_binh</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>tach_condition_khoi_effect</t>
-        </is>
-      </c>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>chap_thuan</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>chap_thuan_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
+          <t>doanh_nghiep_dang_ky_doanh_nghiep_va_cac_bao_cao</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>chấp thuận trên Hệ thống thông tin quốc gia về đăng ký doanh nghiệp</t>
+          <t>Doanh nghiệp đăng ký doanh nghiệp và các báo cáo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `chap_thuan_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `doanh_nghiep_dang_ky_doanh_nghiep_va_cac_bao_cao`.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RULE_ND168_D31_K6_E000267_H565D1BB5E0AC__243ed69455d8ce; RULE_ND168_D31_K6_E000271_H565D1BB5E0AC__515f331279a5a7; RULE_ND168_D31_K6_E000416_HF58B712D1CE4__7867763b848ee0; RULE_ND168_D31_K6_E000419_H46A4A566E7A4__38e6cb2ba88b0e</t>
+          <t>RULE_LUATDN_D8_K3_E000001_H5745E238E6BA__19b1296ca4aca4</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -8200,36 +7944,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>chap_thuan</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>chap_thuan_tru_truong_hop_hoi_dong_thanh_vien_quyet_dinh_thoi_han_khac</t>
+          <t>doanh_nghiep_dang_ky_thay_doi_chu_doanh_nghiep_tu_nhan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>chấp thuận, trừ trường hợp Hội đồng thành viên quyết định thời hạn khác</t>
+          <t>Doanh nghiệp đăng ký thay đổi chủ doanh nghiệp tư nhân</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `chap_thuan_tru_truong_hop_hoi_dong_thanh_vien_quyet_dinh_thoi_han_khac`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `doanh_nghiep_dang_ky_thay_doi_chu_doanh_nghiep_tu_nhan`.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D186_K2_E000128_H978952EE6FD4__271a076b3bf9cb; RULE_LUATDN_D186_K2_E000364_HC305BFE2E363__e1e8bea05ff736; RULE_LUATDN_D186_K2_E000125_H2FC30FD46A92__59df9f03b09822</t>
+          <t>RULE_LUATDN_D192_K4_E000143_HDD7294EC5093__a1844b762d174d</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -8242,11 +7982,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8256,22 +7992,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>co_quan_dang_ky_kinh_doanh_ap_dung_quy_dinh_loai_tru</t>
+          <t>doanh_nghiep_nop_du_so_thue</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cơ quan đăng ký kinh doanh áp dụng quy định loại trừ</t>
+          <t>Doanh nghiệp nộp đủ số thuế</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `co_quan_dang_ky_kinh_doanh_ap_dung_quy_dinh_loai_tru`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `doanh_nghiep_nop_du_so_thue`.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RULE_ND168_D20_K1_A_E000232_HEBA6CEE992E3__33783bcc8ca8c9</t>
+          <t>RULE_LUATDN_D206_K3_E000182_HB3760B0CD551__0c3013b06a8c7b</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -8284,36 +8020,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>co_quan_dang_ky_kinh_doanh_cap_dang_ky_doanh_nghiep_theo_quy_trinh_du_phong</t>
+          <t>duoc_cap_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cơ quan đăng ký kinh doanh cấp đăng ký doanh nghiệp theo quy trình dự phòng</t>
+          <t>Được cấp đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `co_quan_dang_ky_kinh_doanh_cap_dang_ky_doanh_nghiep_theo_quy_trinh_du_phong`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_dang_ky_doanh_nghiep`.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RULE_ND168_D13_K4_E000222_H7575F6E0A298__e3b2e7405f1543</t>
+          <t>RULE_LUATDN_D26_K5_E000011_H3FEBB093524B__f0e073146941eb</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -8326,36 +8058,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>co_quan_dang_ky_kinh_doanh_cap_tinh_thuc_hien_quan_ly_nha_nuoc</t>
+          <t>duoc_cap_dang_ky_doanh_nghiep_theo_quy_trinh_du_phong</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cơ quan đăng ký kinh doanh cấp tỉnh thực hiện quản lý nhà nước</t>
+          <t>Được cấp đăng ký doanh nghiệp theo quy trình dự phòng</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `co_quan_dang_ky_kinh_doanh_cap_tinh_thuc_hien_quan_ly_nha_nuoc`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_dang_ky_doanh_nghiep_theo_quy_trinh_du_phong`.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D215_K2_E000192_HA15EAD4E7536__4a0d8250bffec5</t>
+          <t>RULE_ND168_D13_K4_E000222_H7575F6E0A298__e3b2e7405f1543</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -8368,36 +8096,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>co_quan_dang_ky_kinh_doanh_dang_ky_doanh_nghiep</t>
+          <t>duoc_cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cơ quan đăng ký kinh doanh đăng ký doanh nghiệp</t>
+          <t>Được cấp Giấy chứng nhận đăng ký doanh nghiệp | được cấp Giấy chứng nhận đăng ký doanh nghiệp; được cấp Giấy chứng nhận đăng ký doanh nghiệp; trừ trường hợp Điều lệ công ty hoặc hợp đồng đăng ký mua cổ phần quy định một thời hạn khác ngắn hơn</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `co_quan_dang_ky_kinh_doanh_dang_ky_doanh_nghiep`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_giay_chung_nhan_dang_ky_doanh_nghiep`.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RULE_ND168_D20_K1_A_E000234_H8752DA9084F2__4600286e438dc3; RULE_ND168_D20_K1_A_E000230_HA78F4CA68C80__0e0c127de64957</t>
+          <t>RULE_LUATDN_D113_K1_E000094_HC863DA3A8CBE__234d9c7caeb7b4; RULE_LUATDN_D113_K1_E000085_HABFC666433B3__22c2142f7ac83a; RULE_LUATDN_D113_K1_E000078_H67FF516B0336__96d8cf793c1519; RULE_LUATDN_D205_K2_E000180_HA8EFB2670117__32e45121578765; RULE_LUATDN_D113_K1_E000082_H67FF516B0336__b18dfb4fdee692; RULE_LUATDN_D113_K1_E000083_H4135AC48C5CC__92ac27f8e80f5c; RULE_LUATDN_D113_K1_E000361_H9559D7A7E175__e7c07124cb07f1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8412,34 +8136,34 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>tach_exception_khoi_effect</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>co_quan_dang_ky_kinh_doanh_thanh_phan_ho_so</t>
+          <t>duoc_cap_giay_chung_nhan_dang_ky_doanh_nghiep_moi</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cơ quan đăng ký kinh doanh thành phần hồ sơ</t>
+          <t>Được cấp Giấy chứng nhận đăng ký doanh nghiệp mới</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `co_quan_dang_ky_kinh_doanh_thanh_phan_ho_so`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_giay_chung_nhan_dang_ky_doanh_nghiep_moi`.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RULE_ND168_D15_K4_E000226_H77B8473A5144__f4a8cfe63d7a31</t>
+          <t>RULE_LUATDN_D30_K3_E000031_H683D2BEC0D69__9f7fb709427928</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -8452,36 +8176,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>doanh_nghiep_dang_ky_doanh_nghiep</t>
+          <t>duoc_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Doanh nghiệp đăng ký doanh nghiệp</t>
+          <t>Được cấp Giấy chứng nhận đăng ký hoạt động chi nhánh</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `doanh_nghiep_dang_ky_doanh_nghiep`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh`.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RULE_ND168_D23_K1_K_E000238_H9F0055EDAC32__8b171c4fe8e666; RULE_ND168_D4_K5_E000194_H71B013782AB6__fe65a55a4c30bb</t>
+          <t>RULE_LUATDN_D45_K3_E000041_H54A3724FA902__05e1c142b45446</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -8494,36 +8214,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>doanh_nghiep_dang_ky_doanh_nghiep_va_cac_bao_cao</t>
+          <t>duoc_cap_tinh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Doanh nghiệp đăng ký doanh nghiệp và các báo cáo</t>
+          <t>Được cấp tỉnh cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `doanh_nghiep_dang_ky_doanh_nghiep_va_cac_bao_cao`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_tinh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so`.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D8_K3_E000001_H5745E238E6BA__19b1296ca4aca4</t>
+          <t>RULE_ND168_D31_K3_E000415_HF96DE9D9BF08__715810e59d4772; RULE_ND168_D41_K2_E000425_HEEADD79DF7E1__341dcc712fe43d; RULE_ND168_D42_K2_E000430_H871CDC7A0EBD__6112b7ae8b0e38; RULE_ND168_D43_K5_E000435_HADF045408BC9__6a55deefc5885c; RULE_ND168_D44_K5_E000440_H3776FA482E45__895dd1b8852a0c</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8536,36 +8252,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>doanh_nghiep_dang_ky_thay_doi_chu_doanh_nghiep_tu_nhan</t>
+          <t>duoc_cap_tinh_thuc_hien_quan_ly_nha_nuoc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Doanh nghiệp đăng ký thay đổi chủ doanh nghiệp tư nhân</t>
+          <t>Được cấp tỉnh thực hiện quản lý nhà nước</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `doanh_nghiep_dang_ky_thay_doi_chu_doanh_nghiep_tu_nhan`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_tinh_thuc_hien_quan_ly_nha_nuoc`.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D192_K4_E000143_HDD7294EC5093__a1844b762d174d</t>
+          <t>RULE_LUATDN_D215_K2_E000192_HA15EAD4E7536__4a0d8250bffec5</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8578,36 +8290,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>cap_giay</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>doanh_nghiep_nop_du_so_thue</t>
+          <t>duoc_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Doanh nghiệp nộp đủ số thuế</t>
+          <t>Được cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `doanh_nghiep_nop_du_so_thue`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so`.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D206_K3_E000182_HB3760B0CD551__0c3013b06a8c7b</t>
+          <t>RULE_ND168_D31_K3_E000266_H1509A1A35C79__4bce78214f31d1; RULE_ND168_D41_K2_E000273_H906A9A038A6C__f824edde05271e; RULE_ND168_D42_K2_E000275_H821D573EEDF4__530e6c2ac4eb1f; RULE_ND168_D43_K5_E000277_H0243FD848FE3__802b6f2206ab87; RULE_ND168_D44_K5_E000279_HCA503CFECDA8__aa2d89008e4cec</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8620,36 +8328,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>cap_nhat</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>duoc_cap_dang_ky_doanh_nghiep</t>
+          <t>khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_dong_thoi_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_chi_nhanh_van_phong_dai</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Được cấp đăng ký doanh nghiệp</t>
+          <t>khôi phục Giấy chứng nhận đăng ký doanh nghiệp, đồng thời cập nhật tình trạng pháp lý của doanh nghiệp, chi nhánh, văn phòng đại</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_dang_ky_doanh_nghiep`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_dong_thoi_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_chi_nhanh_van_phong_dai`.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D26_K5_E000011_H3FEBB093524B__f0e073146941eb</t>
+          <t>RULE_ND168_D70_K2_E000315_H76391FA4DF19__fd8923adabc565</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8662,36 +8366,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>cap_nhat</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>duoc_cap_dang_ky_doanh_nghiep_theo_quy_trinh_du_phong</t>
+          <t>khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_dong_thoi_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_chi_nhanh_van_phong_dai_dien_dia_diem_kinh_doanh_trong_co_so_du</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Được cấp đăng ký doanh nghiệp theo quy trình dự phòng</t>
+          <t>khôi phục Giấy chứng nhận đăng ký doanh nghiệp, đồng thời cập nhật tình trạng pháp lý của doanh nghiệp, chi nhánh, văn phòng đại diện, địa điểm kinh doanh trong Cơ sở dữ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_dang_ky_doanh_nghiep_theo_quy_trinh_du_phong`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_dong_thoi_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_chi_nhanh_van_phong_dai_dien_dia_diem_kinh_doanh_trong_co_so_du`.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RULE_ND168_D13_K4_E000222_H7575F6E0A298__e3b2e7405f1543</t>
+          <t>RULE_ND168_D70_K2_E000490_H294525A8FA40__1aeefc8cc68ed5</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8704,36 +8404,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>duoc_cap_giay_chung_nhan_dang_ky_doanh_nghiep</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Được cấp Giấy chứng nhận đăng ký doanh nghiệp | được cấp Giấy chứng nhận đăng ký doanh nghiệp; được cấp Giấy chứng nhận đăng ký doanh nghiệp; trừ trường hợp Điều lệ công ty hoặc hợp đồng đăng ký mua cổ phần quy định một thời hạn khác ngắn hơn</t>
+          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp, Giấy xác nhận về việc thay đổi nội dung</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_giay_chung_nhan_dang_ky_doanh_nghiep`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung`.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D113_K1_E000094_HC863DA3A8CBE__234d9c7caeb7b4; RULE_LUATDN_D113_K1_E000085_HABFC666433B3__22c2142f7ac83a; RULE_LUATDN_D113_K1_E000078_H67FF516B0336__96d8cf793c1519; RULE_LUATDN_D205_K2_E000180_HA8EFB2670117__32e45121578765; RULE_LUATDN_D113_K1_E000082_H67FF516B0336__b18dfb4fdee692; RULE_LUATDN_D113_K1_E000083_H4135AC48C5CC__92ac27f8e80f5c; RULE_LUATDN_D113_K1_E000361_H9559D7A7E175__e7c07124cb07f1</t>
+          <t>RULE_ND168_D69_K8_E000307_H645CB00A88CB__1970f0cce8350d</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8746,36 +8442,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>tach_exception_khoi_effect</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>duoc_cap_giay_chung_nhan_dang_ky_doanh_nghiep_moi</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_k</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Được cấp Giấy chứng nhận đăng ký doanh nghiệp mới</t>
+          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp, Giấy xác nhận về việc thay đổi nội dung đăng ký doanh nghiệp, Giấy xác nhận thông báo tạm ngừng k</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_giay_chung_nhan_dang_ky_doanh_nghiep_moi`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_k`.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D30_K3_E000031_H683D2BEC0D69__9f7fb709427928</t>
+          <t>RULE_ND168_D69_K8_E000308_H645CB00A88CB__6cb2986879ea28; RULE_ND168_D69_K8_E000486_H27C3716A7863__43b7c194143b91</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8788,36 +8480,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>duoc_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_kinh_doanh_giay_xac_nhan_thon</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Được cấp Giấy chứng nhận đăng ký hoạt động chi nhánh</t>
+          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp, Giấy xác nhận về việc thay đổi nội dung đăng ký doanh nghiệp, Giấy xác nhận thông báo tạm ngừng kinh doanh, Giấy xác nhận thôn</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_kinh_doanh_giay_xac_nhan_thon`.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D45_K3_E000041_H54A3724FA902__05e1c142b45446</t>
+          <t>RULE_ND168_D69_K8_E000487_H2A77DF79A945__61915324e2a4e1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8830,36 +8518,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>duoc_cap_thong_tin_duoc_luu_giu_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_phai_nop_phi</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_kinh_doanh_giay_xac_nhan_thong_bao_t</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Được cấp thông tin được lưu giữ trên Hệ thống thông tin quốc gia về đăng ký doanh nghiệp và phải nộp phí</t>
+          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp, Giấy xác nhận về việc thay đổi nội dung đăng ký doanh nghiệp, Giấy xác nhận thông báo tạm ngừng kinh doanh, Giấy xác nhận thông báo t</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_thong_tin_duoc_luu_giu_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep_va_phai_nop_phi`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_kinh_doanh_giay_xac_nhan_thong_bao_t`.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D33_K1_E000040_HBD0F2B965340__e0be59d28bca43</t>
+          <t>RULE_ND168_D69_K8_E000484_H27C3716A7863__9d99e90d01c504</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -8872,36 +8556,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>duoc_cap_tinh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_va_viec_khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Được cấp tỉnh cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ</t>
+          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp và việc khôi phục Giấy chứng nhận đăng ký doanh nghiệp trên Hệ thống thông tin quốc gia về đăng ký</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_tinh_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_va_viec_khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky`.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RULE_ND168_D31_K3_E000415_HF96DE9D9BF08__715810e59d4772; RULE_ND168_D41_K2_E000425_HEEADD79DF7E1__341dcc712fe43d; RULE_ND168_D42_K2_E000430_H871CDC7A0EBD__6112b7ae8b0e38; RULE_ND168_D43_K5_E000435_HADF045408BC9__6a55deefc5885c; RULE_ND168_D44_K5_E000440_H3776FA482E45__895dd1b8852a0c</t>
+          <t>RULE_ND168_D70_K2_E000316_H76391FA4DF19__0b8d819f490a52</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -8914,78 +8594,74 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>duoc_cap_tinh_thuc_hien_quan_ly_nha_nuoc</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Được cấp tỉnh thực hiện quản lý nhà nước</t>
+          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh trong thời hạn 03 ngày làm việc kể từ ngày kết thúc thời hạn giải trình</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_tinh_thuc_hien_quan_ly_nha_nuoc`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh`.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RULE_LUATDN_D215_K2_E000192_HA15EAD4E7536__4a0d8250bffec5</t>
+          <t>RULE_ND168_D107_K4_E000502_HAD9534ACA4E3__ff40d9db87e1fc</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>cao</t>
+          <t>trung_binh</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>tach_condition_khoi_effect</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cap_giay</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>duoc_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Được cấp tỉnh trao giấy tiếp nhận hồ sơ và hẹn trả kết quả cho người nộp hồ sơ</t>
+          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh đồng thời ra thông báo về việc hộ kinh doanh đang làm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `duoc_cap_tinh_trao_giay_tiep_nhan_ho_so_va_hen_tra_ket_qua_cho_nguoi_nop_ho_so`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam`.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RULE_ND168_D31_K3_E000266_H1509A1A35C79__4bce78214f31d1; RULE_ND168_D41_K2_E000273_H906A9A038A6C__f824edde05271e; RULE_ND168_D42_K2_E000275_H821D573EEDF4__530e6c2ac4eb1f; RULE_ND168_D43_K5_E000277_H0243FD848FE3__802b6f2206ab87; RULE_ND168_D44_K5_E000279_HCA503CFECDA8__aa2d89008e4cec</t>
+          <t>RULE_ND168_D107_K8_E000327_H9246BA7D11BB__dac16f19cbbcc1; RULE_ND168_D107_K8_E000335_HE798C4D32E8B__e4edbc88f7a14a</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -8998,36 +8674,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cap_nhat</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_dong_thoi_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_chi_nhanh_van_phong_dai</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_cap_nhat_tinh_t</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>khôi phục Giấy chứng nhận đăng ký doanh nghiệp, đồng thời cập nhật tình trạng pháp lý của doanh nghiệp, chi nhánh, văn phòng đại</t>
+          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh đồng thời ra thông báo về việc hộ kinh doanh đang làm thủ tục chấm dứt hoạt động, cập nhật tình t</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_dong_thoi_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_chi_nhanh_van_phong_dai`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_cap_nhat_tinh_t`.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RULE_ND168_D70_K2_E000315_H76391FA4DF19__fd8923adabc565</t>
+          <t>RULE_ND168_D107_K8_E000328_H9246BA7D11BB__01bdb283d4efa8; RULE_ND168_D107_K8_E000336_HE798C4D32E8B__a51346519b4342; RULE_ND168_D107_K8_E000331_H65C05EF0DADF__a81f4623de28c9</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9040,36 +8712,32 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cap_nhat</t>
+          <t>thu_hoi</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_dong_thoi_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_chi_nhanh_van_phong_dai_dien_dia_diem_kinh_doanh_trong_co_so_du</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_cap_nhat_tinh_trang_phap_ly_cua_ho_kinh_doan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>khôi phục Giấy chứng nhận đăng ký doanh nghiệp, đồng thời cập nhật tình trạng pháp lý của doanh nghiệp, chi nhánh, văn phòng đại diện, địa điểm kinh doanh trong Cơ sở dữ</t>
+          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh đồng thời ra thông báo về việc hộ kinh doanh đang làm thủ tục chấm dứt hoạt động, cập nhật tình trạng pháp lý của hộ kinh doan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_dong_thoi_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_chi_nhanh_van_phong_dai_dien_dia_diem_kinh_doanh_trong_co_so_du`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_cap_nhat_tinh_trang_phap_ly_cua_ho_kinh_doan`.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RULE_ND168_D70_K2_E000490_H294525A8FA40__1aeefc8cc68ed5</t>
+          <t>RULE_ND168_D107_K8_E000514_HF1DC4B5243E5__287d78470bad44</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -9082,11 +8750,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9096,22 +8760,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_va_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_tren_cong_thong_tin_quoc_g</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp, Giấy xác nhận về việc thay đổi nội dung</t>
+          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh và thông báo về việc hộ kinh doanh đang làm thủ tục chấm dứt hoạt động trên Cổng thông tin quốc g</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_va_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_tren_cong_thong_tin_quoc_g`.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RULE_ND168_D69_K8_E000307_H645CB00A88CB__1970f0cce8350d</t>
+          <t>RULE_ND168_D107_K8_E000329_H9246BA7D11BB__149bd3691389fa; RULE_ND168_D107_K8_E000337_HE798C4D32E8B__3fa257eb657871</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -9124,11 +8788,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9138,22 +8798,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_k</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_va_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_tren_cong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp, Giấy xác nhận về việc thay đổi nội dung đăng ký doanh nghiệp, Giấy xác nhận thông báo tạm ngừng k</t>
+          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh và thông báo về việc hộ kinh doanh đang làm thủ tục chấm dứt hoạt động trên Cổng thông tin quốc gia về đăng ký doanh nghiệp</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_k`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_va_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_tren_cong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep`.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RULE_ND168_D69_K8_E000308_H645CB00A88CB__6cb2986879ea28; RULE_ND168_D69_K8_E000486_H27C3716A7863__43b7c194143b91</t>
+          <t>RULE_ND168_D107_K8_E000504_HE6BBDAF42D70__3340ce83b0c5f4</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -9166,11 +8826,7 @@
           <t>cao</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9180,413 +8836,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_kinh_doanh_giay_xac_nhan_thon</t>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh_van_phong_dai_dien</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp, Giấy xác nhận về việc thay đổi nội dung đăng ký doanh nghiệp, Giấy xác nhận thông báo tạm ngừng kinh doanh, Giấy xác nhận thôn</t>
+          <t>thu hồi Giấy chứng nhận đăng ký hoạt động chi nhánh, văn phòng đại diện trong thời hạn 03 ngày làm việc kể từ ngày kết thúc thời hạn giải trình</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_kinh_doanh_giay_xac_nhan_thon`.</t>
+          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh_van_phong_dai_dien`.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RULE_ND168_D69_K8_E000487_H2A77DF79A945__61915324e2a4e1</t>
+          <t>RULE_ND168_D71_K3_E000496_HD4B75A6952A5__ca660bf58d6b4b</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>khong</t>
+          <t>co</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>cao</t>
+          <t>trung_binh</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_kinh_doanh_giay_xac_nhan_thong_bao_t</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp, Giấy xác nhận về việc thay đổi nội dung đăng ký doanh nghiệp, Giấy xác nhận thông báo tạm ngừng kinh doanh, Giấy xác nhận thông báo t</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_giay_xac_nhan_ve_viec_thay_doi_noi_dung_dang_ky_doanh_nghiep_giay_xac_nhan_thong_bao_tam_ngung_kinh_doanh_giay_xac_nhan_thong_bao_t`.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D69_K8_E000484_H27C3716A7863__9d99e90d01c504</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>cao</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_va_viec_khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>thu hồi Giấy chứng nhận đăng ký doanh nghiệp và việc khôi phục Giấy chứng nhận đăng ký doanh nghiệp trên Hệ thống thông tin quốc gia về đăng ký</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_doanh_nghiep_va_viec_khoi_phuc_giay_chung_nhan_dang_ky_doanh_nghiep_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky`.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D70_K2_E000316_H76391FA4DF19__0b8d819f490a52</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>cao</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh trong thời hạn 03 ngày làm việc kể từ ngày kết thúc thời hạn giải trình</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh`.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D107_K4_E000502_HAD9534ACA4E3__ff40d9db87e1fc</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>trung_binh</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>tach_condition_khoi_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh đồng thời ra thông báo về việc hộ kinh doanh đang làm</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam`.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D107_K8_E000327_H9246BA7D11BB__dac16f19cbbcc1; RULE_ND168_D107_K8_E000335_HE798C4D32E8B__e4edbc88f7a14a</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>cao</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_cap_nhat_tinh_t</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh đồng thời ra thông báo về việc hộ kinh doanh đang làm thủ tục chấm dứt hoạt động, cập nhật tình t</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_cap_nhat_tinh_t`.</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D107_K8_E000328_H9246BA7D11BB__01bdb283d4efa8; RULE_ND168_D107_K8_E000336_HE798C4D32E8B__a51346519b4342; RULE_ND168_D107_K8_E000331_H65C05EF0DADF__a81f4623de28c9</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>cao</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_cap_nhat_tinh_trang_phap_ly_cua_ho_kinh_doan</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh đồng thời ra thông báo về việc hộ kinh doanh đang làm thủ tục chấm dứt hoạt động, cập nhật tình trạng pháp lý của hộ kinh doan</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_dong_thoi_ra_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_cap_nhat_tinh_trang_phap_ly_cua_ho_kinh_doan`.</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D107_K8_E000514_HF1DC4B5243E5__287d78470bad44</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>cao</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_va_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_tren_cong_thong_tin_quoc_g</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh và thông báo về việc hộ kinh doanh đang làm thủ tục chấm dứt hoạt động trên Cổng thông tin quốc g</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_va_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_tren_cong_thong_tin_quoc_g`.</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D107_K8_E000329_H9246BA7D11BB__149bd3691389fa; RULE_ND168_D107_K8_E000337_HE798C4D32E8B__3fa257eb657871</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>cao</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_va_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_tren_cong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh và thông báo về việc hộ kinh doanh đang làm thủ tục chấm dứt hoạt động trên Cổng thông tin quốc gia về đăng ký doanh nghiệp</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_va_thong_bao_ve_viec_ho_kinh_doanh_dang_lam_thu_tuc_cham_dut_hoat_dong_tren_cong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep`.</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D107_K8_E000504_HE6BBDAF42D70__3340ce83b0c5f4</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>khong</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>cao</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>thu_hoi</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>thu_hoi_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh_van_phong_dai_dien</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>thu hồi Giấy chứng nhận đăng ký hoạt động chi nhánh, văn phòng đại diện trong thời hạn 03 ngày làm việc kể từ ngày kết thúc thời hạn giải trình</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Kết quả/hậu quả (đã tách điều kiện/ngoại lệ nếu có). `thu_hoi_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh_van_phong_dai_dien`.</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RULE_ND168_D71_K3_E000496_HD4B75A6952A5__ca660bf58d6b4b</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>trung_binh</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
         <is>
           <t>tach_condition_khoi_effect</t>
         </is>
@@ -11791,7 +11069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11831,6 +11109,632 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>effect_vocabulary</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>duoc_cap_giay_chung_nhan_dang_ky_doanh_nghiep_tru_truong_hop_dieu_le_cong_ty_hoac_hop_dong_dang_ky_mua_co_phan_quy_dinh_mot_thoi_han_khac_ngan_hon</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>tru_truong_hop_dieu_le_cong_ty_hoac_hop_dong_dang_ky_mua_co_phan_quy_dinh_mot_thoi_han_khac_ngan_hon</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>được cấp Giấy chứng nhận đăng ký doanh nghiệp, trừ trường hợp Điều lệ công ty hoặc hợp đồng đăng ký mua cổ phần quy định một thời hạn khác ngắn hơn</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tach_exception_condition_khoi_effect</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>RULE_LUATDN_D113_K1_E000082_H67FF516B0336__b18dfb4fdee692; RULE_LUATDN_D113_K1_E000083_H4135AC48C5CC__92ac27f8e80f5c; RULE_LUATDN_D113_K1_E000361_H9559D7A7E175__e7c07124cb07f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>effect_vocabulary</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>chap_thuan_tru_truong_hop_hoi_dong_thanh_vien_quyet_dinh_thoi_han_khac</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>tru_truong_hop_hoi_dong_thanh_vien_quyet_dinh_thoi_han_khac</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>chấp thuận, trừ trường hợp Hội đồng thành viên quyết định thời hạn khác</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>tach_exception_condition_khoi_effect</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RULE_LUATDN_D186_K2_E000128_H978952EE6FD4__271a076b3bf9cb; RULE_LUATDN_D186_K2_E000364_HC305BFE2E363__e1e8bea05ff736; RULE_LUATDN_D186_K2_E000125_H2FC30FD46A92__59df9f03b09822</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>effect_vocabulary</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cap_giay_chung_nhan_dang_ky_doanh_nghiep_neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>cấp Giấy chứng nhận đăng ký doanh nghiệp nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>tach_exception_condition_khoi_effect</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RULE_LUATDN_D205_K2_E000171_HC103AB968CE3__db7af93bea0162</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>effect_vocabulary</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cap_giay_chung_nhan_dang_ky_doanh_nghiep_neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghie</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>neu_co_du_dieu_kien_quy_dinh_tai_khoan_1_dieu_nay_va_cap_nhat_tinh_trang_phap_ly_cua_doanh_nghiep_tren_co_so_du_lieu_quoc_gia_ve_dang_ky_doanh_nghie</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>cấp Giấy chứng nhận đăng ký doanh nghiệp nếu có đủ điều kiện quy định tại khoản 1 Điều này và cập nhật tình trạng pháp lý của doanh nghiệp trên Cơ sở dữ liệu quốc gia về đăng ký doanh nghiệ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>tach_exception_condition_khoi_effect</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>RULE_LUATDN_D205_K2_E000376_HDE4D11047D02__d8fcb45eefe40d</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>effect_vocabulary</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cap_giay_chung_nhan_dang_ky_doanh_nghiep_neu_co_du_dieu_kien_quy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>neu_co_du_dieu_kien_quy</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>cấp Giấy chứng nhận đăng ký doanh nghiệp nếu có đủ điều kiện quy</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>tach_exception_condition_khoi_effect</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RULE_LUATDN_D205_K2_E000174_HBB868040B12A__747ded761e8875</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>effect_vocabulary</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_ho_kinh_doanh_trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han_giai_trinh</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han_giai_trinh</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>thu hồi Giấy chứng nhận đăng ký hộ kinh doanh trong thời hạn 03 ngày làm việc kể từ ngày kết thúc thời hạn giải trình</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>tach_exception_condition_khoi_effect</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>RULE_ND168_D107_K4_E000502_HAD9534ACA4E3__ff40d9db87e1fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>effect_vocabulary</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cham_dut_hoat_dong_doi_voi_chi_nhanh_van_phong_dai_dien_dia_diem_kinh_doanh</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>doi_voi_chi_nhanh_van_phong_dai_dien_dia_diem_kinh_doanh</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>chấm dứt hoạt động đối với chi nhánh, văn phòng đại diện, địa điểm kinh doanh</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>tach_exception_condition_khoi_effect</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RULE_ND168_D118_K3_E000522_H0811C24751E0__7fb44d85940b04; RULE_ND168_D118_K3_E000341_H6839229D9C6F__6f008278ee22c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>effect_vocabulary</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>thu_hoi_giay_chung_nhan_dang_ky_hoat_dong_chi_nhanh_van_phong_dai_dien_trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han_giai_trinh</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>trong_thoi_han_03_ngay_lam_viec_ke_tu_ngay_ket_thuc_thoi_han_giai_trinh</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>thu hồi Giấy chứng nhận đăng ký hoạt động chi nhánh, văn phòng đại diện trong thời hạn 03 ngày làm việc kể từ ngày kết thúc thời hạn giải trình</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>tach_exception_condition_khoi_effect</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RULE_ND168_D71_K3_E000496_HD4B75A6952A5__ca660bf58d6b4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>discourse_or_condition</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>object_vocabulary</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>phai_co_cac_giay_to_sau_day</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>phải có các giấy tờ sau đây | phải có các giấy tờ sau đây:</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>loai_condition_hoac_scope_khoi_object</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>RULE_ND168_D28_K7_E000248_H189EC3F188B6__506b814bf616a9; RULE_ND168_D28_K7_E000410_HAB891EF8FB58__9c53376c4e0d7b; RULE_ND168_D28_K7_E000409_HAB891EF8FB58__b4611058cb4d7c; RULE_ND168_D28_K7_E000411_HAB891EF8FB58__9271c5cad72e01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>discourse_or_condition</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>object_vocabulary</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>khi_dang_ky_thanh_lap_doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>khi đăng ký thành lập doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>loai_condition_hoac_scope_khoi_object</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RULE_LUATDN_D120_K2_E000110_H2F74D053E9ED__e3455c07586f9b; RULE_LUATDN_D120_K2_E000106_H50EB455F10E0__d9e773edb1f1e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>discourse_or_condition</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>object_vocabulary</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>khi_trinh_dai_hoi_dong_co_dong_xem_xet</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>khi trình Đại hội đồng cổ đông xem xét</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>loai_condition_hoac_scope_khoi_object</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>RULE_LUATDN_D175_K2_E000122_H3A810D8013F8__cecb075395e7d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>discourse_or_condition</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>object_vocabulary</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>hop_dong_da_ky_voi_khach_hang_va_nguoi_lao_dong</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>hợp đồng đã ký với khách hàng và người lao động</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>loai_condition_hoac_scope_khoi_object</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>RULE_LUATDN_D206_K3_E000183_HB3760B0CD551__fa214a6f1d0709</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>discourse_or_condition</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>object_vocabulary</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>tru_truong_hop_doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>trừ trường hợp doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>loai_condition_hoac_scope_khoi_object</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RULE_LUATDN_D206_K3_E000184_HB3760B0CD551__d9cc7b2a45cf2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>discourse_or_condition</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>object_vocabulary</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>hop_dong_da_ky_voi_khach_hang_va_nguoi_lao_dong_tru_truong_hop_doanh_nghiep_chu_no_khach_hang_va_nguoi</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>hợp đồng đã ký với khách hàng và người lao động, trừ trường hợp doanh nghiệp, chủ nợ, khách hàng và người</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>loai_condition_hoac_scope_khoi_object</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>RULE_LUATDN_D206_K3_E000182_HB3760B0CD551__0c3013b06a8c7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>discourse_or_condition</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>object_vocabulary</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>khi_thay_doi_noi_dung_giay_chung_nhan_dang_ky_doanh_nghiep_quy_dinh_tai_dieu_28_cua_luat_nay</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>khi thay đổi nội dung Giấy chứng nhận đăng ký doanh nghiệp quy định tại Điều 28 của Luật này</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>loai_condition_hoac_scope_khoi_object</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>RULE_LUATDN_D30_K1_E000020_H4E002511683E__bc79ef05e292ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>discourse_or_condition</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>object_vocabulary</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>khi_ho_so_dang_ky_doanh_nghiep_chua_duoc_chap_thuan_tren_he_thong_thong_tin_quoc_gia_ve_dang_ky_doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>khi hồ sơ đăng ký doanh nghiệp chưa được chấp thuận trên Hệ thống thông tin quốc gia về đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>loai_condition_hoac_scope_khoi_object</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>RULE_ND168_D31_K6_E000267_H565D1BB5E0AC__243ed69455d8ce; RULE_ND168_D31_K6_E000271_H565D1BB5E0AC__515f331279a5a7; RULE_ND168_D31_K6_E000416_HF58B712D1CE4__7867763b848ee0; RULE_ND168_D31_K6_E000419_H46A4A566E7A4__38e6cb2ba88b0e; RULE_ND168_D31_K6_E000421_H46A4A566E7A4__0907921944a235</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>discourse_or_condition</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>object_vocabulary</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>truong_hop_doanh_nghiep_cap_nhat</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>trường hợp doanh nghiệp cập nhật</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>loai_condition_hoac_scope_khoi_object</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>RULE_ND168_D57_K3_E000299_HA471205F1C6F__44c27f4eae6de3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>discourse_or_condition</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>object_vocabulary</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>van_ban_giai_trinh_cua_doanh_nghiep_ve_ly_do_dang_ky_thay_doi_kem_ho_so_dang_ky_thay_doi_khi_dang_ky_phuc_vu_giai_the</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>văn bản giải trình của doanh nghiệp về lý do đăng ký thay đổi (kèm hồ sơ đăng ký thay đổi khi đăng ký phục vụ giải thể)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>loai_condition_hoac_scope_khoi_object</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>RULE_ND168_D59_K2_B_E000479_H6CE5F7A93C8B__e80d74b1b90e68; RULE_ND168_D59_K2_B_E000480_H6CE5F7A93C8B__56e9128f42f85d</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
